--- a/event_registration_forms/033_restaurant_host_hostess_application_form--event_registration_forms.xlsx
+++ b/event_registration_forms/033_restaurant_host_hostess_application_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Emergency Relation</t>
+          <t>Emergency Relationship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Work Experience</t>
+          <t>Work Experience Details</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Availability Availability</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Availability Availability Frequency</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'host/hostess'}</t>
+          <t>host/hostess</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Host/Hostess'}</t>
+          <t>Host/Hostess</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'server'}</t>
+          <t>server</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Server'}</t>
+          <t>Server</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'chef'}</t>
+          <t>chef</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Chef'}</t>
+          <t>Chef</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'owner'}</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Owner'}</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'german'}</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'German'}</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'mandarin'}</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'Mandarin'}</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'name':_'seasonal'}</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'name': 'Seasonal'}</t>
+          <t>Seasonal</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'name':_'casual'}</t>
+          <t>casual</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'name': 'Casual'}</t>
+          <t>Casual</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'name': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'name':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'name': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'name':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'name': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'name':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'name': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'name':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'name': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'name':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'name': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'name':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'name': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
